--- a/output/graficos_regionales/plot_regional_serie_i_ingr_m_2020_los_rios.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_m_2020_los_rios.xlsx
@@ -288,7 +288,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:40</t>
+    <t xml:space="preserve">2026-10-05 02:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -723,10 +723,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>655007.62</v>
+        <v>655007.63</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>804762.62</v>
+        <v>804762.63</v>
       </c>
     </row>
     <row r="5">
@@ -737,7 +737,7 @@
         <v>665082.56</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>799364.12</v>
+        <v>799364.13</v>
       </c>
     </row>
     <row r="6">
@@ -822,7 +822,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>716441.62</v>
+        <v>716441.63</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>876986.31</v>
@@ -836,7 +836,7 @@
         <v>667307</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>826816.62</v>
+        <v>826816.63</v>
       </c>
     </row>
     <row r="15">
@@ -844,7 +844,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>660018.62</v>
+        <v>660018.63</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>816360.81</v>
@@ -877,7 +877,7 @@
         <v>19</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>706499.62</v>
+        <v>706499.63</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>844285.88</v>
@@ -913,7 +913,7 @@
         <v>709514.69</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>849932.62</v>
+        <v>849932.63</v>
       </c>
     </row>
     <row r="22">
@@ -965,7 +965,7 @@
         <v>27</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>713630.12</v>
+        <v>713630.13</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>877882.31</v>
@@ -998,10 +998,10 @@
         <v>30</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>754691.12</v>
+        <v>754691.13</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>885489.12</v>
+        <v>885489.13</v>
       </c>
     </row>
     <row r="30">
@@ -1009,10 +1009,10 @@
         <v>31</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>751750.12</v>
+        <v>751750.13</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>873830.12</v>
+        <v>873830.13</v>
       </c>
     </row>
     <row r="31">
@@ -1053,7 +1053,7 @@
         <v>35</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>815600.12</v>
+        <v>815600.13</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>930460.56</v>
@@ -1097,7 +1097,7 @@
         <v>39</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>767274.12</v>
+        <v>767274.13</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>917146.44</v>
@@ -1141,7 +1141,7 @@
         <v>43</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>792541.12</v>
+        <v>792541.13</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>927625.75</v>
@@ -1166,7 +1166,7 @@
         <v>815287.31</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>953641.12</v>
+        <v>953641.13</v>
       </c>
     </row>
     <row r="45">
@@ -1218,7 +1218,7 @@
         <v>50</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>886298.12</v>
+        <v>886298.13</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>1049309.75</v>
@@ -1251,7 +1251,7 @@
         <v>53</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>870790.12</v>
+        <v>870790.13</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>1019749.94</v>
@@ -1287,7 +1287,7 @@
         <v>898895.31</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>1048559.62</v>
+        <v>1048559.63</v>
       </c>
     </row>
     <row r="56">
@@ -1298,7 +1298,7 @@
         <v>897546</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>1059287.62</v>
+        <v>1059287.63</v>
       </c>
     </row>
     <row r="57">
@@ -1328,7 +1328,7 @@
         <v>60</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>921478.12</v>
+        <v>921478.13</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>1086115.25</v>
@@ -1342,7 +1342,7 @@
         <v>935134.75</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>1093564.62</v>
+        <v>1093564.63</v>
       </c>
     </row>
     <row r="61">
@@ -1350,7 +1350,7 @@
         <v>62</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>992703.62</v>
+        <v>992703.63</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>1183065.88</v>
@@ -1364,7 +1364,7 @@
         <v>972966</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>1145616.62</v>
+        <v>1145616.63</v>
       </c>
     </row>
     <row r="63">
@@ -1394,7 +1394,7 @@
         <v>66</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>1003275.62</v>
+        <v>1003275.63</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>1168289.25</v>
@@ -1419,7 +1419,7 @@
         <v>1017185.88</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>1184430.62</v>
+        <v>1184430.63</v>
       </c>
     </row>
     <row r="68">
@@ -1438,7 +1438,7 @@
         <v>70</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>1016363.12</v>
+        <v>1016363.13</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>1186515.5</v>
@@ -1460,7 +1460,7 @@
         <v>72</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>1029557.62</v>
+        <v>1029557.63</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>1202545</v>
@@ -1471,7 +1471,7 @@
         <v>73</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>1051608.62</v>
+        <v>1051608.63</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>1219650.75</v>
@@ -1482,7 +1482,7 @@
         <v>74</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>1087873.62</v>
+        <v>1087873.63</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>1284570.75</v>
@@ -1518,7 +1518,7 @@
         <v>1062174</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>1240434.12</v>
+        <v>1240434.13</v>
       </c>
     </row>
     <row r="77">
@@ -1548,10 +1548,10 @@
         <v>80</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>1085318.62</v>
+        <v>1085318.63</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>1253268.12</v>
+        <v>1253268.13</v>
       </c>
     </row>
     <row r="80">
@@ -1562,7 +1562,7 @@
         <v>1092075</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>1274861.62</v>
+        <v>1274861.63</v>
       </c>
     </row>
     <row r="81">
@@ -1584,7 +1584,7 @@
         <v>1146125.88</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>1327655.12</v>
+        <v>1327655.13</v>
       </c>
     </row>
     <row r="83">
